--- a/XlsxSharp.Tests/Resource/Other/PivotTable/TableProps/Property_layout_sets_layout_of_pivot_table_and_all_fields-outline.xlsx
+++ b/XlsxSharp.Tests/Resource/Other/PivotTable/TableProps/Property_layout_sets_layout_of_pivot_table_and_all_fields-outline.xlsx
@@ -1,73 +1,73 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:workbookPr codeName="ThisWorkbook"/>
-  <x:bookViews>
-    <x:workbookView firstSheet="0" activeTab="1"/>
-  </x:bookViews>
-  <x:sheets>
-    <x:sheet name="Sheet1" sheetId="1" r:id="rId2"/>
-    <x:sheet name="Sheet2" sheetId="2" r:id="rId3"/>
-  </x:sheets>
-  <x:definedNames/>
-  <x:calcPr calcId="125725"/>
-  <x:pivotCaches>
-    <x:pivotCache cacheId="0" r:id="rId6"/>
-  </x:pivotCaches>
-</x:workbook>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <workbookPr codeName="ThisWorkbook"/>
+  <bookViews>
+    <workbookView firstSheet="0" activeTab="1"/>
+  </bookViews>
+  <sheets>
+    <sheet r:id="rId1" name="Sheet1" sheetId="1"/>
+    <sheet r:id="rId2" name="Sheet2" sheetId="2"/>
+  </sheets>
+  <definedNames/>
+  <calcPr calcId="125725"/>
+  <pivotCaches>
+    <pivotCache cacheId="0" r:id="rId5"/>
+  </pivotCaches>
+</workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Size</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Month</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Season</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Price</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Currency</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cake</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Small</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Jan</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Winter</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Pie</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Large</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Feb</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Summer</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CZK</x:t>
-  </x:si>
-</x:sst>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Size</t>
+  </si>
+  <si>
+    <t>Month</t>
+  </si>
+  <si>
+    <t>Season</t>
+  </si>
+  <si>
+    <t>Price</t>
+  </si>
+  <si>
+    <t>Currency</t>
+  </si>
+  <si>
+    <t>Cake</t>
+  </si>
+  <si>
+    <t>Small</t>
+  </si>
+  <si>
+    <t>Jan</t>
+  </si>
+  <si>
+    <t>Winter</t>
+  </si>
+  <si>
+    <t>EUR</t>
+  </si>
+  <si>
+    <t>Pie</t>
+  </si>
+  <si>
+    <t>Large</t>
+  </si>
+  <si>
+    <t>Feb</t>
+  </si>
+  <si>
+    <t>Summer</t>
+  </si>
+  <si>
+    <t>CZK</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -119,7 +119,83 @@
 </styleSheet>
 </file>
 
-<file path=xl/pivotTables/pivotTable.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" createdVersion="5" refreshedVersion="5" minRefreshableVersion="3" saveData="1" refreshOnLoad="1">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:F4" sheet="Sheet1"/>
+  </cacheSource>
+  <cacheFields>
+    <cacheField name="Name">
+      <sharedItems count="2">
+        <s v="Cake"/>
+        <s v="Pie"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Size">
+      <sharedItems count="2">
+        <s v="Small"/>
+        <s v="Large"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Month">
+      <sharedItems count="2">
+        <s v="Jan"/>
+        <s v="Feb"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Season">
+      <sharedItems count="2">
+        <s v="Winter"/>
+        <s v="Summer"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Price">
+      <sharedItems count="3" containsNumber="1" containsInteger="1" minValue="3" maxValue="9" containsSemiMixedTypes="0" containsString="0">
+        <n v="9"/>
+        <n v="7"/>
+        <n v="3"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Currency">
+      <sharedItems count="2">
+        <s v="EUR"/>
+        <s v="CZK"/>
+      </sharedItems>
+    </cacheField>
+  </cacheFields>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="xr">
+  <r>
+    <s v="Cake"/>
+    <s v="Small"/>
+    <s v="Jan"/>
+    <s v="Winter"/>
+    <n v="9"/>
+    <s v="EUR"/>
+  </r>
+  <r>
+    <s v="Pie"/>
+    <s v="Small"/>
+    <s v="Jan"/>
+    <s v="Winter"/>
+    <n v="7"/>
+    <s v="EUR"/>
+  </r>
+  <r>
+    <s v="Cake"/>
+    <s v="Large"/>
+    <s v="Feb"/>
+    <s v="Summer"/>
+    <n v="3"/>
+    <s v="CZK"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="pivot table" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" compact="0" outline="1" outlineData="1" compactData="0">
   <location ref="A1" firstHeaderRow="0" firstDataRow="0" firstDataCol="0"/>
   <pivotFields count="6">
@@ -454,193 +530,117 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
-  <x:dimension ref="A1:F4"/>
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:sheetData>
-    <x:row r="1" spans="1:6">
-      <x:c r="A1" s="0" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B1" s="0" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C1" s="0" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D1" s="0" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E1" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F1" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:6">
-      <x:c r="A2" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B2" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C2" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D2" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="E2" s="0">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="F2" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:6">
-      <x:c r="A3" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="B3" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C3" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D3" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="E3" s="0">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="F3" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:6">
-      <x:c r="A4" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B4" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C4" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D4" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="E4" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="F4" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
-</x:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="0" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="0">
+        <v>9</v>
+      </c>
+      <c r="F2" s="0" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="0">
+        <v>7</v>
+      </c>
+      <c r="F3" s="0" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="0">
+        <v>3</v>
+      </c>
+      <c r="F4" s="0" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <pageSetup paperSize="1" orientation="default" pageOrder="downThenOver" cellComments="none" errors="displayed" blackAndWhite="0" draft="0" scale="100"/>
+  <headerFooter/>
+  <tableParts count="0"/>
+</worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
-  <x:dimension ref="A1"/>
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="15.710625" style="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData/>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
-</x:worksheet>
-</file>
-
-<file path=pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:pivotCacheDefinition xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r:id="rId1" saveData="1" refreshOnLoad="1" createdVersion="5" refreshedVersion="5" minRefreshableVersion="3">
-  <x:cacheSource type="worksheet">
-    <x:worksheetSource ref="A1:F4" sheet="Sheet1"/>
-  </x:cacheSource>
-  <x:cacheFields>
-    <x:cacheField name="Name">
-      <x:sharedItems count="2">
-        <x:s v="Cake"/>
-        <x:s v="Pie"/>
-      </x:sharedItems>
-    </x:cacheField>
-    <x:cacheField name="Size">
-      <x:sharedItems count="2">
-        <x:s v="Small"/>
-        <x:s v="Large"/>
-      </x:sharedItems>
-    </x:cacheField>
-    <x:cacheField name="Month">
-      <x:sharedItems count="2">
-        <x:s v="Jan"/>
-        <x:s v="Feb"/>
-      </x:sharedItems>
-    </x:cacheField>
-    <x:cacheField name="Season">
-      <x:sharedItems count="2">
-        <x:s v="Winter"/>
-        <x:s v="Summer"/>
-      </x:sharedItems>
-    </x:cacheField>
-    <x:cacheField name="Price">
-      <x:sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="3" maxValue="9" count="3">
-        <x:n v="9"/>
-        <x:n v="7"/>
-        <x:n v="3"/>
-      </x:sharedItems>
-    </x:cacheField>
-    <x:cacheField name="Currency">
-      <x:sharedItems count="2">
-        <x:s v="EUR"/>
-        <x:s v="CZK"/>
-      </x:sharedItems>
-    </x:cacheField>
-  </x:cacheFields>
-</x:pivotCacheDefinition>
-</file>
-
-<file path=pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="xr">
-  <r>
-    <s v="Cake"/>
-    <s v="Small"/>
-    <s v="Jan"/>
-    <s v="Winter"/>
-    <n v="9"/>
-    <s v="EUR"/>
-  </r>
-  <r>
-    <s v="Pie"/>
-    <s v="Small"/>
-    <s v="Jan"/>
-    <s v="Winter"/>
-    <n v="7"/>
-    <s v="EUR"/>
-  </r>
-  <r>
-    <s v="Cake"/>
-    <s v="Large"/>
-    <s v="Feb"/>
-    <s v="Summer"/>
-    <n v="3"/>
-    <s v="CZK"/>
-  </r>
-</pivotCacheRecords>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" style="0" customWidth="1" width="15.710625"/>
+  </cols>
+  <sheetData/>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <pageSetup paperSize="1" orientation="default" pageOrder="downThenOver" cellComments="none" errors="displayed" blackAndWhite="0" draft="0" scale="100"/>
+  <headerFooter/>
+  <tableParts count="0"/>
+</worksheet>
 </file>